--- a/tame_output/ON/bt/strategyON_20231125.xlsx
+++ b/tame_output/ON/bt/strategyON_20231125.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,16 +605,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,17 +623,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>92.2%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.0%</t>
+          <t>101.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.2%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.8%</t>
+          <t>131.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>125.6%</t>
+          <t>125.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.6%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1791"/>
+  <dimension ref="A1:G1792"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.145659693631203</v>
+        <v>3.14626574482338</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42719,6 +42719,29 @@
       </c>
       <c r="G1791" t="n">
         <v>4.378153363235525</v>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" s="2" t="n">
+        <v>45254</v>
+      </c>
+      <c r="B1792" t="n">
+        <v>3.157863149879231</v>
+      </c>
+      <c r="C1792" t="n">
+        <v>3.07155002509494</v>
+      </c>
+      <c r="D1792" t="n">
+        <v>1.551617836401165</v>
+      </c>
+      <c r="E1792" t="n">
+        <v>3.69184073534166</v>
+      </c>
+      <c r="F1792" t="n">
+        <v>2.174515430377279</v>
+      </c>
+      <c r="G1792" t="n">
+        <v>4.376259283321309</v>
       </c>
     </row>
   </sheetData>
